--- a/apps/web/public/templates/报价参数导入模板.xlsx
+++ b/apps/web/public/templates/报价参数导入模板.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>报价参数导入模板（三期 · Excel 列映射）</t>
   </si>
@@ -24,6 +24,30 @@
   </si>
   <si>
     <t>用法：按下面 4 个 Sheet 填数据，上传到「智能识别 → 参数表导入」即可一键生成报价参数。</t>
+  </si>
+  <si>
+    <t>· 模具清单：每行一套模具（前/后模钢材、模芯长宽高、腔数、热流道、滑块斜顶、寿命…）</t>
+  </si>
+  <si>
+    <t>· 注塑件清单：每行一个注塑件（材料、单件重量、数量、机台时薪、周期、损耗率…）</t>
+  </si>
+  <si>
+    <t>· 公共参数：整单一份（运输箱长/宽/高、运费单价、运输区域）</t>
+  </si>
+  <si>
+    <t>· 其他费用：每行一条自由费用（名称 + 金额 + 备注）</t>
+  </si>
+  <si>
+    <t>列名会自动识别（支持「模芯长 / 模芯长度 / CoreLength」等多种写法）；钢材/材料可填编码或中文名。</t>
+  </si>
+  <si>
+    <t>比例类参数请填小数：5% 写 0.05（写「5%」也能识别，但写「5」会被当成 500% 并给出提示）。</t>
+  </si>
+  <si>
+    <t>利润率 / 税率即使填了也以「配置中心」为准，本表不会覆盖。</t>
+  </si>
+  <si>
+    <t>识别不到的列会提示你人工确认，不会悄悄丢数据。</t>
   </si>
   <si>
     <t>模具编号</t>
@@ -165,13 +189,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -194,8 +225,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,25 +568,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -569,72 +647,72 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="P1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>500</v>
@@ -686,39 +764,39 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>0.18</v>
@@ -749,25 +827,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -806,24 +884,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>500</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web/public/templates/报价参数导入模板.xlsx
+++ b/apps/web/public/templates/报价参数导入模板.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="说明" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="模具清单" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="注塑件清单" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="公共参数" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="整单参数" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="其他费用" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
   <si>
     <t>报价参数导入模板（三期 · Excel 列映射）</t>
   </si>
@@ -32,7 +32,7 @@
     <t>· 注塑件清单：每行一个注塑件（材料、单件重量、数量、机台时薪、周期、损耗率…）</t>
   </si>
   <si>
-    <t>· 公共参数：整单一份（运输箱长/宽/高、运费单价、运输区域）</t>
+    <t>· 整单参数：整单一份（运输箱长/宽/高、运费单价、运输区域等整单统一项）</t>
   </si>
   <si>
     <t>· 其他费用：每行一条自由费用（名称 + 金额 + 备注）</t>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>识别不到的列会提示你人工确认，不会悄悄丢数据。</t>
+  </si>
+  <si>
+    <t>【2026-09 变更】原「公共参数」Sheet 已并入「整单参数」；两种叫法都能识别，老表不用改也能用。</t>
   </si>
   <si>
     <t>模具编号</t>
@@ -189,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -204,13 +207,23 @@
     <font>
       <sz val="11"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10.5"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E40AF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -225,10 +238,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,10 +584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -632,6 +648,16 @@
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -645,74 +671,74 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M1" t="s">
+      <c r="L1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N1" t="s">
+      <c r="M1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O1" t="s">
+      <c r="N1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="P1" t="s">
+      <c r="O1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="P1" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>500</v>
@@ -762,41 +788,41 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="3" t="s">
         <v>40</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2">
         <v>0.18</v>
@@ -825,27 +851,27 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -882,26 +908,26 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="3" t="s">
         <v>53</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>500</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
